--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484314_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484314_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5431</v>
+        <v>2.4304</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5356</v>
+        <v>2.2322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0076</v>
+        <v>0.1982</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0412</v>
@@ -610,13 +610,13 @@
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5524</v>
+        <v>-0.6651</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1294</v>
+        <v>-0.1739</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6818</v>
+        <v>-0.4912</v>
       </c>
       <c r="V2" t="n">
         <v>2.16</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2072</v>
+        <v>1.0904</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4814</v>
+        <v>1.5825</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2742</v>
+        <v>-0.4921</v>
       </c>
       <c r="G3" t="n">
         <v>1.0988</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9817</v>
+        <v>-1.0985</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6657</v>
+        <v>-0.5646</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.316</v>
+        <v>-0.5339</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3046</v>
+        <v>0.0063</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0331</v>
+        <v>-0.4959</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7285</v>
+        <v>0.5022</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3279</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3663</v>
+        <v>1.7588</v>
       </c>
       <c r="I4" t="n">
         <v>-1.0385</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6774</v>
+        <v>1.0049</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3111</v>
+        <v>1.6385</v>
       </c>
       <c r="L4" t="n">
         <v>-0.6336000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3496</v>
+        <v>-0.2846</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0553</v>
+        <v>0.1203</v>
       </c>
       <c r="O4" t="n">
         <v>-0.4049</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-1.1046</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.524</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.5806</v>
+      </c>
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>0.9767</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.3907</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2504</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.6411</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.6093</v>
-      </c>
       <c r="W4" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2268</v>
+        <v>0.0012</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1215</v>
+        <v>2.7297</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3483</v>
+        <v>-2.7285</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0329</v>
+        <v>0.3279</v>
       </c>
       <c r="H5" t="n">
-        <v>1.317</v>
+        <v>1.3663</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2841</v>
+        <v>-1.0385</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8161</v>
+        <v>0.6774</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8854</v>
+        <v>1.3111</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9307</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7832</v>
+        <v>-0.3496</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5684</v>
+        <v>0.0553</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2148</v>
+        <v>-0.4049</v>
       </c>
       <c r="P5" t="n">
         <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7071</v>
+        <v>-0.694</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7179</v>
+        <v>-0.0529</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0108</v>
+        <v>-0.6411</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5294</v>
+        <v>-0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5294</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4138</v>
+        <v>-0.3685</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6981000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2843</v>
+        <v>-1.3483</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7203000000000001</v>
+        <v>1.0329</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7588</v>
+        <v>1.317</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0385</v>
+        <v>-0.2841</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0049</v>
+        <v>2.8161</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6385</v>
+        <v>1.8854</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.9307</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2846</v>
+        <v>-1.7832</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1203</v>
+        <v>-0.5684</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4049</v>
+        <v>-1.2148</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5248</v>
+        <v>-0.8488</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.8596</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7985</v>
+        <v>0.0108</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.5294</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5294</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8991</v>
+        <v>-0.714</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8543</v>
+        <v>1.7126</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7534</v>
+        <v>-2.4266</v>
       </c>
       <c r="G7" t="n">
         <v>1.0587</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9596</v>
+        <v>-0.7745</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4153</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5443</v>
+        <v>-0.2175</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5842</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9537</v>
+        <v>-0.8155</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3584</v>
+        <v>0.1065</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5952</v>
+        <v>-0.922</v>
       </c>
       <c r="G8" t="n">
         <v>0.1499</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3473</v>
+        <v>-0.2091</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1499</v>
+        <v>-0.6849</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8027</v>
+        <v>0.4758</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3656</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.697</v>
+        <v>-1.1425</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4446</v>
+        <v>0.8084</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1416</v>
+        <v>-1.9509</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2863</v>
@@ -1156,13 +1156,13 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0917</v>
+        <v>-0.5372</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0289</v>
+        <v>-0.665</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.1278</v>
       </c>
       <c r="V9" t="n">
         <v>0.853</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5791</v>
+        <v>-2.4313</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6684</v>
+        <v>-1.4662</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9107</v>
+        <v>-0.9651</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3432</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4313</v>
+        <v>-1.2835</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5846</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6445</v>
+        <v>-0.6989</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1779</v>
+        <v>-7.6464</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4832</v>
+        <v>-5.6249</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6947</v>
+        <v>-2.0215</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7421</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1987</v>
+        <v>-0.6672</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5969</v>
+        <v>-0.7386</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3982</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.307</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.8925</v>
+        <v>-9.5899</v>
       </c>
       <c r="E12" t="n">
-        <v>2.262400000000001</v>
+        <v>2.564699999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.1547</v>
+        <v>-12.1546</v>
       </c>
       <c r="G12" t="n">
         <v>-0.02430000000000021</v>
@@ -1369,7 +1369,7 @@
         <v>4.9129</v>
       </c>
       <c r="L12" t="n">
-        <v>7.4241</v>
+        <v>7.424099999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-12.3611</v>
@@ -1390,13 +1390,13 @@
         <v>14.6506</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.1853</v>
+        <v>-7.8825</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.7079</v>
+        <v>-5.405099999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4773</v>
+        <v>-2.4774</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6597</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.0951</v>
+        <v>7.2049</v>
       </c>
       <c r="E13" t="n">
-        <v>8.381600000000001</v>
+        <v>6.7637</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7135</v>
+        <v>0.4412</v>
       </c>
       <c r="G13" t="n">
         <v>2.3497</v>
@@ -1468,13 +1468,13 @@
         <v>2.7348</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6785</v>
+        <v>1.7883</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2206</v>
+        <v>0.6027</v>
       </c>
       <c r="U13" t="n">
-        <v>1.458</v>
+        <v>1.1856</v>
       </c>
       <c r="V13" t="n">
         <v>0.3321</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2002</v>
+        <v>3.1578</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8276</v>
+        <v>2.2209</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3726</v>
+        <v>0.9369</v>
       </c>
       <c r="G14" t="n">
         <v>0.7272</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6683</v>
+        <v>0.6259</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6219</v>
+        <v>0.0152</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0464</v>
+        <v>0.6107</v>
       </c>
       <c r="V14" t="n">
         <v>1.2186</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3573</v>
+        <v>3.0189</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7085</v>
+        <v>2.5062</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6488</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1221</v>
@@ -1624,13 +1624,13 @@
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9369</v>
+        <v>1.5985</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.7499</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9849</v>
+        <v>0.8487</v>
       </c>
       <c r="V15" t="n">
         <v>3.3238</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9676</v>
+        <v>2.4187</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7574</v>
+        <v>2.263</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2102</v>
+        <v>0.1557</v>
       </c>
       <c r="G16" t="n">
         <v>3.594</v>
@@ -1702,13 +1702,13 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0171</v>
+        <v>0.434</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7125</v>
+        <v>-0.2069</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6954</v>
+        <v>0.6409</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2186</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4673</v>
+        <v>0.8953</v>
       </c>
       <c r="E17" t="n">
-        <v>0.616</v>
+        <v>0.7171</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1487</v>
+        <v>0.1782</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2096</v>
@@ -1780,13 +1780,13 @@
         <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1315</v>
+        <v>0.2965</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1732</v>
+        <v>-0.0721</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0417</v>
+        <v>0.3686</v>
       </c>
       <c r="V17" t="n">
         <v>0.2224</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1035</v>
+        <v>0.3135</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5894</v>
+        <v>0.6905</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4859</v>
+        <v>-0.377</v>
       </c>
       <c r="G18" t="n">
         <v>1.7984</v>
@@ -1858,13 +1858,13 @@
         <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2817</v>
+        <v>0.4918</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0083</v>
+        <v>0.1095</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2734</v>
+        <v>0.3823</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6093</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2553</v>
+        <v>-0.153</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8522</v>
+        <v>0.2982</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1075</v>
+        <v>-0.4512</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4246</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0051</v>
+        <v>-2.0814</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4297</v>
+        <v>1.2542</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9086</v>
+        <v>-0.0733</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3863</v>
+        <v>-1.3277</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2949</v>
+        <v>1.2544</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.484</v>
+        <v>-0.7538</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6188</v>
+        <v>-0.7536</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1348</v>
+        <v>-0.0002</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.6741</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7016</v>
+        <v>0.3715</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1496</v>
+        <v>0.3026</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5575</v>
+        <v>-0.4283</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1063</v>
+        <v>-1.9247</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4512</v>
+        <v>1.4964</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.4063</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0814</v>
+        <v>0.3756</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2542</v>
+        <v>-0.7819</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0733</v>
+        <v>-0.6055</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3277</v>
+        <v>0.0409</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2544</v>
+        <v>-0.6465</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7538</v>
+        <v>0.1992</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7536</v>
+        <v>0.3346</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0002</v>
+        <v>-0.1354</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2696</v>
+        <v>-0.022</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.033</v>
+        <v>-0.3425</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3026</v>
+        <v>0.3205</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7667</v>
+        <v>-0.4848</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.127</v>
+        <v>1.6499</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3602</v>
+        <v>-2.1347</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4063</v>
+        <v>0.4246</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3756</v>
+        <v>-1.0051</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7819</v>
+        <v>1.4297</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6055</v>
+        <v>0.9086</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0409</v>
+        <v>-0.3863</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6465</v>
+        <v>1.2949</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1992</v>
+        <v>-0.484</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3346</v>
+        <v>-0.6188</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>0.1348</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3604</v>
+        <v>0.6218</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5447</v>
+        <v>0.4994</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1843</v>
+        <v>0.1224</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8467</v>
+        <v>-2.1856</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7014</v>
+        <v>-1.0947</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1453</v>
+        <v>-1.0908</v>
       </c>
       <c r="G22" t="n">
         <v>0.2814</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3527</v>
+        <v>1.0139</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.154</v>
+        <v>0.4527</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5067</v>
+        <v>0.5612</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9414</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8724</v>
+        <v>-3.865</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6433</v>
+        <v>-1.9355</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.229</v>
+        <v>-1.9294</v>
       </c>
       <c r="G23" t="n">
         <v>-6.586</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.345</v>
+        <v>0.6624</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4099</v>
+        <v>0.2979</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0649</v>
+        <v>0.3645</v>
       </c>
       <c r="V23" t="n">
         <v>0.8865</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.892399999999999</v>
+        <v>9.8924</v>
       </c>
       <c r="E24" t="n">
-        <v>12.1547</v>
+        <v>12.1546</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2623</v>
+        <v>-2.2621</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02419999999999956</v>
+        <v>0.02419999999999867</v>
       </c>
       <c r="H24" t="n">
         <v>-1.3237</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3481</v>
+        <v>1.348100000000001</v>
       </c>
       <c r="J24" t="n">
         <v>12.3612</v>
@@ -2314,7 +2314,7 @@
         <v>-4.913</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.423999999999999</v>
+        <v>-7.424</v>
       </c>
       <c r="P24" t="n">
         <v>-0.9768000000000003</v>
@@ -2326,13 +2326,13 @@
         <v>13.674</v>
       </c>
       <c r="S24" t="n">
-        <v>8.185</v>
+        <v>8.1852</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4772</v>
+        <v>2.4773</v>
       </c>
       <c r="U24" t="n">
-        <v>5.7079</v>
+        <v>5.707999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>2.6596</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484314_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484314_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>-2.7145</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.5294</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.5842</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.6428</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.5842</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.5842</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-11.9668</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1657,67 +1728,72 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4187</v>
+        <v>2.1349</v>
       </c>
       <c r="E16" t="n">
-        <v>2.263</v>
+        <v>2.1349</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1557</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.594</v>
+        <v>2.1349</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6813</v>
+        <v>0.921</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9127</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4233</v>
+        <v>2.1349</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1051</v>
+        <v>0.921</v>
       </c>
       <c r="L16" t="n">
-        <v>3.3182</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8293</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4239</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4054</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.434</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2069</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6409</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,11 +1956,16 @@
       <c r="X18" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.153</v>
+        <v>0.2838</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2982</v>
+        <v>0.1281</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4512</v>
+        <v>0.1557</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8270999999999999</v>
+        <v>1.4591</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0814</v>
+        <v>-0.2397</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2542</v>
+        <v>1.6988</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0733</v>
+        <v>2.2884</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3277</v>
+        <v>0.1842</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2544</v>
+        <v>2.1042</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7538</v>
+        <v>-0.8293</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7536</v>
+        <v>-0.4239</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0002</v>
+        <v>-0.4054</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6741</v>
+        <v>0.434</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3715</v>
+        <v>-0.2069</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3026</v>
+        <v>0.6409</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4283</v>
+        <v>-0.153</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9247</v>
+        <v>0.2982</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4964</v>
+        <v>-0.4512</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4063</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3756</v>
+        <v>-2.0814</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7819</v>
+        <v>1.2542</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6055</v>
+        <v>-0.0733</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0409</v>
+        <v>-1.3277</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6465</v>
+        <v>1.2544</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1992</v>
+        <v>-0.7538</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3346</v>
+        <v>-0.7536</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>-0.0002</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.022</v>
+        <v>0.6741</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3425</v>
+        <v>0.3715</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3205</v>
+        <v>0.3026</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4848</v>
+        <v>-0.4283</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6499</v>
+        <v>-1.9247</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1347</v>
+        <v>1.4964</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4246</v>
+        <v>-0.4063</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0051</v>
+        <v>0.3756</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4297</v>
+        <v>-0.7819</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9086</v>
+        <v>-0.6055</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3863</v>
+        <v>0.0409</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2949</v>
+        <v>-0.6465</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.484</v>
+        <v>0.1992</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6188</v>
+        <v>0.3346</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1348</v>
+        <v>-0.1354</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6218</v>
+        <v>-0.022</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4994</v>
+        <v>-0.3425</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1224</v>
+        <v>0.3205</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1856</v>
+        <v>-0.4848</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0947</v>
+        <v>1.6499</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0908</v>
+        <v>-2.1347</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2814</v>
+        <v>0.4246</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7403999999999999</v>
+        <v>-1.0051</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4589</v>
+        <v>1.4297</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1055</v>
+        <v>0.9086</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0246</v>
+        <v>-0.3863</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0809</v>
+        <v>1.2949</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.484</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2842</v>
+        <v>-0.6188</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5399</v>
+        <v>0.1348</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5395</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0139</v>
+        <v>0.6218</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4527</v>
+        <v>0.4994</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5612</v>
+        <v>0.1224</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9414</v>
+        <v>-0.5545</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.865</v>
+        <v>-2.1856</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9355</v>
+        <v>-1.0947</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9294</v>
+        <v>-1.0908</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.586</v>
+        <v>0.2814</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.824</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7619</v>
+        <v>-0.4589</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.9479</v>
+        <v>1.1055</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2653</v>
+        <v>1.0246</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6826</v>
+        <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.638</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5587</v>
+        <v>-0.2842</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0793</v>
+        <v>-0.5399</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1721</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6624</v>
+        <v>1.0139</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2979</v>
+        <v>0.4527</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3645</v>
+        <v>0.5612</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8865</v>
+        <v>-0.9414</v>
       </c>
       <c r="W23" t="n">
-        <v>2.7145</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,152 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.865</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.9355</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.9294</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-6.586</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.824</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.7619</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-4.9479</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-2.2653</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2.6826</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.638</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.0793</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.7145</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484314_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>9.8924</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>12.1546</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>-2.2621</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G25" t="n">
         <v>0.02419999999999867</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>-1.3237</v>
       </c>
-      <c r="I24" t="n">
-        <v>1.348100000000001</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I25" t="n">
+        <v>1.348200000000001</v>
+      </c>
+      <c r="J25" t="n">
         <v>12.3612</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.5891</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K25" t="n">
+        <v>3.5892</v>
+      </c>
+      <c r="L25" t="n">
         <v>8.772000000000002</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>-12.3368</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>-4.913</v>
       </c>
-      <c r="O24" t="n">
-        <v>-7.424</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="O25" t="n">
+        <v>-7.423999999999999</v>
+      </c>
+      <c r="P25" t="n">
         <v>-0.9768000000000003</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>-14.6505</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>13.674</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>8.1852</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>2.4773</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>5.707999999999999</v>
       </c>
-      <c r="V24" t="n">
-        <v>2.6596</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="V25" t="n">
+        <v>2.659599999999999</v>
+      </c>
+      <c r="W25" t="n">
         <v>11.9668</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>-9.3071</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
